--- a/FL-corrections-structure/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/FL-corrections-structure/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-08T19:18:35+00:00</t>
+    <t>2026-03-11T17:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
